--- a/assets/excel/pl/wskazniki_globalne.xlsx
+++ b/assets/excel/pl/wskazniki_globalne.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sidwab\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\niewiadomskaew\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A02E27CA-B9D5-4795-B79A-6C7994800DED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E28BA13A-10C8-455E-9635-4F7F556BBD3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cele_1-17" sheetId="1" r:id="rId1"/>
@@ -1690,7 +1690,7 @@
     <t>100% rejestracja zgonów</t>
   </si>
   <si>
-    <t>Ostatnia aktualizacja: 10-02-2026, 09:34</t>
+    <t>Ostatnia aktualizacja: 24-02-2026, 08:37</t>
   </si>
 </sst>
 </file>

--- a/assets/excel/pl/wskazniki_globalne.xlsx
+++ b/assets/excel/pl/wskazniki_globalne.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\niewiadomskaew\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dregerj\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E28BA13A-10C8-455E-9635-4F7F556BBD3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{448DFAFF-73ED-4BA2-AA1A-EFADCB9FACB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cele_1-17" sheetId="1" r:id="rId1"/>
@@ -1690,7 +1690,7 @@
     <t>100% rejestracja zgonów</t>
   </si>
   <si>
-    <t>Ostatnia aktualizacja: 24-02-2026, 08:37</t>
+    <t>Ostatnia aktualizacja: 10-03-2026, 12:36</t>
   </si>
 </sst>
 </file>
@@ -2244,6 +2244,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:U479"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -6265,49 +6268,51 @@
       <c r="E68" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="F68" s="4">
+      <c r="F68" s="5">
         <v>451.8</v>
       </c>
-      <c r="G68" s="4">
+      <c r="G68" s="5">
         <v>440.9</v>
       </c>
-      <c r="H68" s="4">
+      <c r="H68" s="5">
         <v>460.8</v>
       </c>
-      <c r="I68" s="4">
+      <c r="I68" s="5">
         <v>460.8</v>
       </c>
-      <c r="J68" s="4">
+      <c r="J68" s="5">
         <v>441.1</v>
       </c>
-      <c r="K68" s="4">
+      <c r="K68" s="5">
         <v>469</v>
       </c>
-      <c r="L68" s="4">
+      <c r="L68" s="5">
         <v>437.1</v>
       </c>
-      <c r="M68" s="4">
+      <c r="M68" s="5">
         <v>434.8</v>
       </c>
-      <c r="N68" s="4">
+      <c r="N68" s="5">
         <v>437.2</v>
       </c>
-      <c r="O68" s="4">
+      <c r="O68" s="5">
         <v>421</v>
       </c>
-      <c r="P68" s="4">
+      <c r="P68" s="5">
         <v>457.2</v>
       </c>
-      <c r="Q68" s="4">
+      <c r="Q68" s="5">
         <v>475.8</v>
       </c>
-      <c r="R68" s="4">
+      <c r="R68" s="5">
         <v>426.2</v>
       </c>
-      <c r="S68" s="4">
+      <c r="S68" s="5">
         <v>400.4</v>
       </c>
-      <c r="T68" s="3"/>
+      <c r="T68" s="5">
+        <v>400.02</v>
+      </c>
       <c r="U68" s="2" t="s">
         <v>27</v>
       </c>
@@ -6370,7 +6375,9 @@
       <c r="S69" s="4">
         <v>25.7</v>
       </c>
-      <c r="T69" s="3"/>
+      <c r="T69" s="4">
+        <v>24.3</v>
+      </c>
       <c r="U69" s="2" t="s">
         <v>27</v>
       </c>
@@ -6433,7 +6440,9 @@
       <c r="S70" s="4">
         <v>264.39999999999998</v>
       </c>
-      <c r="T70" s="3"/>
+      <c r="T70" s="4">
+        <v>265.39999999999998</v>
+      </c>
       <c r="U70" s="2" t="s">
         <v>27</v>
       </c>
@@ -6488,15 +6497,17 @@
         <v>22.9</v>
       </c>
       <c r="Q71" s="4">
-        <v>25.4</v>
+        <v>25.5</v>
       </c>
       <c r="R71" s="4">
-        <v>24.6</v>
+        <v>26.6</v>
       </c>
       <c r="S71" s="4">
-        <v>25.7</v>
-      </c>
-      <c r="T71" s="3"/>
+        <v>25.8</v>
+      </c>
+      <c r="T71" s="4">
+        <v>25.3</v>
+      </c>
       <c r="U71" s="2" t="s">
         <v>27</v>
       </c>
@@ -6559,7 +6570,9 @@
       <c r="S72" s="4">
         <v>12.1</v>
       </c>
-      <c r="T72" s="3"/>
+      <c r="T72" s="4">
+        <v>11.6</v>
+      </c>
       <c r="U72" s="2" t="s">
         <v>27</v>
       </c>
@@ -6622,7 +6635,9 @@
       <c r="S73" s="4">
         <v>21.4</v>
       </c>
-      <c r="T73" s="3"/>
+      <c r="T73" s="4">
+        <v>20.7</v>
+      </c>
       <c r="U73" s="2" t="s">
         <v>27</v>
       </c>
@@ -6685,7 +6700,9 @@
       <c r="S74" s="4">
         <v>3.4</v>
       </c>
-      <c r="T74" s="3"/>
+      <c r="T74" s="4">
+        <v>3.1</v>
+      </c>
       <c r="U74" s="2" t="s">
         <v>27</v>
       </c>
@@ -6813,7 +6830,9 @@
       <c r="S76" s="4">
         <v>5</v>
       </c>
-      <c r="T76" s="3"/>
+      <c r="T76" s="4">
+        <v>5.0999999999999996</v>
+      </c>
       <c r="U76" s="2" t="s">
         <v>118</v>
       </c>
@@ -7683,9 +7702,11 @@
         <v>34.799999999999997</v>
       </c>
       <c r="S92" s="4">
-        <v>37.6</v>
-      </c>
-      <c r="T92" s="3"/>
+        <v>36.5</v>
+      </c>
+      <c r="T92" s="4">
+        <v>37.700000000000003</v>
+      </c>
       <c r="U92" s="2" t="s">
         <v>27</v>
       </c>
@@ -7728,9 +7749,11 @@
         <v>9.1999999999999993</v>
       </c>
       <c r="S93" s="4">
-        <v>9.8000000000000007</v>
-      </c>
-      <c r="T93" s="3"/>
+        <v>9.6</v>
+      </c>
+      <c r="T93" s="4">
+        <v>9.9</v>
+      </c>
       <c r="U93" s="2" t="s">
         <v>27</v>
       </c>
@@ -7775,7 +7798,9 @@
       <c r="S94" s="4">
         <v>65</v>
       </c>
-      <c r="T94" s="3"/>
+      <c r="T94" s="4">
+        <v>66.3</v>
+      </c>
       <c r="U94" s="2" t="s">
         <v>27</v>
       </c>
@@ -13793,49 +13818,49 @@
         <v>277</v>
       </c>
       <c r="F219" s="5">
-        <v>0.56999999999999995</v>
+        <v>0.59</v>
       </c>
       <c r="G219" s="5">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="H219" s="5">
-        <v>0.57999999999999996</v>
+        <v>0.59</v>
       </c>
       <c r="I219" s="5">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="J219" s="5">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="K219" s="5">
         <v>0.69</v>
       </c>
       <c r="L219" s="5">
-        <v>0.67</v>
+        <v>0.69</v>
       </c>
       <c r="M219" s="5">
         <v>0.69</v>
       </c>
       <c r="N219" s="5">
-        <v>0.72</v>
+        <v>0.71</v>
       </c>
       <c r="O219" s="5">
+        <v>0.78</v>
+      </c>
+      <c r="P219" s="5">
+        <v>0.77</v>
+      </c>
+      <c r="Q219" s="5">
         <v>0.81</v>
       </c>
-      <c r="P219" s="5">
-        <v>0.81</v>
-      </c>
-      <c r="Q219" s="5">
-        <v>0.86</v>
-      </c>
       <c r="R219" s="5">
-        <v>0.98</v>
+        <v>0.85</v>
       </c>
       <c r="S219" s="5">
-        <v>1.18</v>
+        <v>0.9</v>
       </c>
       <c r="T219" s="5">
-        <v>1.38</v>
+        <v>0.97</v>
       </c>
       <c r="U219" s="2" t="s">
         <v>268</v>
@@ -23220,49 +23245,49 @@
         <v>277</v>
       </c>
       <c r="F376" s="5">
-        <v>0.56999999999999995</v>
+        <v>0.59</v>
       </c>
       <c r="G376" s="5">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="H376" s="5">
-        <v>0.57999999999999996</v>
+        <v>0.59</v>
       </c>
       <c r="I376" s="5">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="J376" s="5">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="K376" s="5">
         <v>0.69</v>
       </c>
       <c r="L376" s="5">
-        <v>0.67</v>
+        <v>0.69</v>
       </c>
       <c r="M376" s="5">
         <v>0.69</v>
       </c>
       <c r="N376" s="5">
-        <v>0.72</v>
+        <v>0.71</v>
       </c>
       <c r="O376" s="5">
+        <v>0.78</v>
+      </c>
+      <c r="P376" s="5">
+        <v>0.77</v>
+      </c>
+      <c r="Q376" s="5">
         <v>0.81</v>
       </c>
-      <c r="P376" s="5">
-        <v>0.81</v>
-      </c>
-      <c r="Q376" s="5">
-        <v>0.86</v>
-      </c>
       <c r="R376" s="5">
-        <v>0.98</v>
+        <v>0.85</v>
       </c>
       <c r="S376" s="5">
-        <v>1.18</v>
+        <v>0.9</v>
       </c>
       <c r="T376" s="5">
-        <v>1.38</v>
+        <v>0.97</v>
       </c>
       <c r="U376" s="2" t="s">
         <v>268</v>
@@ -29063,7 +29088,7 @@
     <hyperlink ref="A2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.39370078740157499" right="0.39370078740157499" top="0.39370078740157499" bottom="0.39370078740157499" header="0.39370078740157499" footer="0.39370078740157499"/>
-  <pageSetup paperSize="9" scale="70" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" scale="71" fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
   <headerFooter alignWithMargins="0"/>
   <drawing r:id="rId3"/>
 </worksheet>

--- a/assets/excel/pl/wskazniki_globalne.xlsx
+++ b/assets/excel/pl/wskazniki_globalne.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dregerj\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{448DFAFF-73ED-4BA2-AA1A-EFADCB9FACB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{092CF30F-2E71-4038-A78A-47FACE76C744}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -862,7 +862,7 @@
     <t>8.4.1 Produktywność zasobów - ZASTĘPCZY!</t>
   </si>
   <si>
-    <t>euro na kilogram [euro/kg]</t>
+    <t>euro (w cenach stałych z 2015 r.)/kg</t>
   </si>
   <si>
     <t>8.4.2 Krajowa Konsumpcja Materialna (DMC)</t>
@@ -1690,7 +1690,7 @@
     <t>100% rejestracja zgonów</t>
   </si>
   <si>
-    <t>Ostatnia aktualizacja: 10-03-2026, 12:36</t>
+    <t>Ostatnia aktualizacja: 17-03-2026, 07:50</t>
   </si>
 </sst>
 </file>
@@ -2244,9 +2244,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
   <dimension ref="A1:U479"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -29088,7 +29085,7 @@
     <hyperlink ref="A2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.39370078740157499" right="0.39370078740157499" top="0.39370078740157499" bottom="0.39370078740157499" header="0.39370078740157499" footer="0.39370078740157499"/>
-  <pageSetup paperSize="9" scale="71" fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" scale="71" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
   <headerFooter alignWithMargins="0"/>
   <drawing r:id="rId3"/>
 </worksheet>

--- a/assets/excel/pl/wskazniki_globalne.xlsx
+++ b/assets/excel/pl/wskazniki_globalne.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dregerj\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sidwab\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{092CF30F-2E71-4038-A78A-47FACE76C744}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64D82AC3-290D-4ABD-8377-14A462A84488}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -652,7 +652,7 @@
     <t>5.2.1 Odsetek kobiet w wieku 18-74 lata, które doświadczyły przemocy fizycznej, seksualnej lub psychicznej ze strony obecnego lub byłego partnera - ZASTĘPCZY!</t>
   </si>
   <si>
-    <t>Agencja Praw Podstawowych Unii Europejskiej</t>
+    <t>Eurostat, Agencja Praw Podstawowych Unii Europejskiej</t>
   </si>
   <si>
     <t>5.3.1 Liczba zawartych związków małżeńskich, w których kobieta w dniu ślubu nie miała ukończonych 18 lat - ZASTĘPCZY!</t>
@@ -868,6 +868,9 @@
     <t>8.4.2 Krajowa Konsumpcja Materialna (DMC)</t>
   </si>
   <si>
+    <t>ogółem w tysiącach</t>
+  </si>
+  <si>
     <t>tony</t>
   </si>
   <si>
@@ -1303,9 +1306,6 @@
     <t>12.2.2 Krajowa Konsumpcja Materialna (DMC)</t>
   </si>
   <si>
-    <t>tys. ton, tony</t>
-  </si>
-  <si>
     <t>12.4.1 Liczba krajów będących stroną wielostronnych umów środowiskowych dotyczących odpadów niebezpiecznych i innych substancji chemicznych, w związku z którymi należy wypełniać zobowiązania w zakresie przekazywania informacji wymaganych odpowiednimi umowami.</t>
   </si>
   <si>
@@ -1690,7 +1690,7 @@
     <t>100% rejestracja zgonów</t>
   </si>
   <si>
-    <t>Ostatnia aktualizacja: 17-03-2026, 07:50</t>
+    <t>Ostatnia aktualizacja: 24-03-2026, 11:45</t>
   </si>
 </sst>
 </file>
@@ -10696,9 +10696,7 @@
       </c>
       <c r="F155" s="3"/>
       <c r="G155" s="3"/>
-      <c r="H155" s="6">
-        <v>2</v>
-      </c>
+      <c r="H155" s="3"/>
       <c r="I155" s="3"/>
       <c r="J155" s="3"/>
       <c r="K155" s="3"/>
@@ -10707,7 +10705,9 @@
       <c r="N155" s="3"/>
       <c r="O155" s="3"/>
       <c r="P155" s="3"/>
-      <c r="Q155" s="3"/>
+      <c r="Q155" s="4">
+        <v>14.6</v>
+      </c>
       <c r="R155" s="3"/>
       <c r="S155" s="3"/>
       <c r="T155" s="3"/>
@@ -11732,7 +11732,9 @@
         <v>46.1</v>
       </c>
       <c r="S177" s="3"/>
-      <c r="T177" s="3"/>
+      <c r="T177" s="4">
+        <v>50.2</v>
+      </c>
       <c r="U177" s="2" t="s">
         <v>27</v>
       </c>
@@ -11781,7 +11783,9 @@
         <v>33.1</v>
       </c>
       <c r="S178" s="3"/>
-      <c r="T178" s="3"/>
+      <c r="T178" s="4">
+        <v>33.700000000000003</v>
+      </c>
       <c r="U178" s="2" t="s">
         <v>27</v>
       </c>
@@ -11830,7 +11834,9 @@
         <v>42.4</v>
       </c>
       <c r="S179" s="3"/>
-      <c r="T179" s="3"/>
+      <c r="T179" s="4">
+        <v>44.1</v>
+      </c>
       <c r="U179" s="2" t="s">
         <v>27</v>
       </c>
@@ -11879,7 +11885,9 @@
         <v>32.299999999999997</v>
       </c>
       <c r="S180" s="3"/>
-      <c r="T180" s="3"/>
+      <c r="T180" s="4">
+        <v>32.9</v>
+      </c>
       <c r="U180" s="2" t="s">
         <v>27</v>
       </c>
@@ -11928,7 +11936,9 @@
         <v>56.3</v>
       </c>
       <c r="S181" s="3"/>
-      <c r="T181" s="3"/>
+      <c r="T181" s="4">
+        <v>57</v>
+      </c>
       <c r="U181" s="2" t="s">
         <v>27</v>
       </c>
@@ -11977,7 +11987,9 @@
         <v>35.4</v>
       </c>
       <c r="S182" s="3"/>
-      <c r="T182" s="3"/>
+      <c r="T182" s="4">
+        <v>36.6</v>
+      </c>
       <c r="U182" s="2" t="s">
         <v>27</v>
       </c>
@@ -12026,7 +12038,9 @@
         <v>59.7</v>
       </c>
       <c r="S183" s="3"/>
-      <c r="T183" s="3"/>
+      <c r="T183" s="4">
+        <v>59.6</v>
+      </c>
       <c r="U183" s="2" t="s">
         <v>27</v>
       </c>
@@ -13874,10 +13888,10 @@
         <v>24</v>
       </c>
       <c r="D220" s="3" t="s">
-        <v>25</v>
+        <v>279</v>
       </c>
       <c r="E220" s="3" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F220" s="4">
         <v>627714.30000000005</v>
@@ -13939,10 +13953,10 @@
         <v>24</v>
       </c>
       <c r="D221" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="E221" s="3" t="s">
         <v>280</v>
-      </c>
-      <c r="E221" s="3" t="s">
-        <v>279</v>
       </c>
       <c r="F221" s="5">
         <v>16.5</v>
@@ -13998,7 +14012,7 @@
         <v>272</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C222" s="2" t="s">
         <v>32</v>
@@ -14007,7 +14021,7 @@
         <v>25</v>
       </c>
       <c r="E222" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F222" s="5">
         <v>21.98</v>
@@ -14047,7 +14061,7 @@
         <v>272</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C223" s="2" t="s">
         <v>32</v>
@@ -14056,7 +14070,7 @@
         <v>33</v>
       </c>
       <c r="E223" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F223" s="5">
         <v>22.89</v>
@@ -14096,7 +14110,7 @@
         <v>272</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C224" s="2" t="s">
         <v>32</v>
@@ -14105,7 +14119,7 @@
         <v>34</v>
       </c>
       <c r="E224" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F224" s="5">
         <v>21</v>
@@ -14145,16 +14159,16 @@
         <v>272</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D225" s="3" t="s">
         <v>229</v>
       </c>
       <c r="E225" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F225" s="5">
         <v>43.51</v>
@@ -14194,16 +14208,16 @@
         <v>272</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C226" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="D226" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="E226" s="3" t="s">
         <v>283</v>
-      </c>
-      <c r="D226" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="E226" s="3" t="s">
-        <v>282</v>
       </c>
       <c r="F226" s="5">
         <v>31.84</v>
@@ -14243,16 +14257,16 @@
         <v>272</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C227" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="D227" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="E227" s="3" t="s">
         <v>283</v>
-      </c>
-      <c r="D227" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="E227" s="3" t="s">
-        <v>282</v>
       </c>
       <c r="F227" s="5">
         <v>21.77</v>
@@ -14292,16 +14306,16 @@
         <v>272</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C228" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="D228" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="E228" s="3" t="s">
         <v>283</v>
-      </c>
-      <c r="D228" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="E228" s="3" t="s">
-        <v>282</v>
       </c>
       <c r="F228" s="5">
         <v>17.649999999999999</v>
@@ -14341,16 +14355,16 @@
         <v>272</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C229" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="D229" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="E229" s="3" t="s">
         <v>283</v>
-      </c>
-      <c r="D229" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="E229" s="3" t="s">
-        <v>282</v>
       </c>
       <c r="F229" s="5">
         <v>12.44</v>
@@ -14390,16 +14404,16 @@
         <v>272</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C230" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="D230" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="E230" s="3" t="s">
         <v>283</v>
-      </c>
-      <c r="D230" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="E230" s="3" t="s">
-        <v>282</v>
       </c>
       <c r="F230" s="5">
         <v>12.82</v>
@@ -14439,16 +14453,16 @@
         <v>272</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C231" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="D231" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="E231" s="3" t="s">
         <v>283</v>
-      </c>
-      <c r="D231" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="E231" s="3" t="s">
-        <v>282</v>
       </c>
       <c r="F231" s="5">
         <v>16.059999999999999</v>
@@ -14488,16 +14502,16 @@
         <v>272</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C232" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="D232" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="E232" s="3" t="s">
         <v>283</v>
-      </c>
-      <c r="D232" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="E232" s="3" t="s">
-        <v>282</v>
       </c>
       <c r="F232" s="5">
         <v>17.239999999999998</v>
@@ -14537,16 +14551,16 @@
         <v>272</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C233" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="D233" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="E233" s="3" t="s">
         <v>283</v>
-      </c>
-      <c r="D233" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="E233" s="3" t="s">
-        <v>282</v>
       </c>
       <c r="F233" s="5">
         <v>12.22</v>
@@ -14586,16 +14600,16 @@
         <v>272</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C234" s="2" t="s">
         <v>212</v>
       </c>
       <c r="D234" s="3" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E234" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F234" s="5">
         <v>13.71</v>
@@ -14635,7 +14649,7 @@
         <v>272</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C235" s="2" t="s">
         <v>212</v>
@@ -14644,7 +14658,7 @@
         <v>181</v>
       </c>
       <c r="E235" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F235" s="5">
         <v>20.66</v>
@@ -14684,7 +14698,7 @@
         <v>272</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C236" s="2" t="s">
         <v>212</v>
@@ -14693,7 +14707,7 @@
         <v>182</v>
       </c>
       <c r="E236" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F236" s="5">
         <v>24.33</v>
@@ -14733,7 +14747,7 @@
         <v>272</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C237" s="2" t="s">
         <v>212</v>
@@ -14742,7 +14756,7 @@
         <v>183</v>
       </c>
       <c r="E237" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F237" s="5">
         <v>22.3</v>
@@ -14782,16 +14796,16 @@
         <v>272</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C238" s="2" t="s">
         <v>212</v>
       </c>
       <c r="D238" s="3" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E238" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F238" s="5">
         <v>22.61</v>
@@ -14831,16 +14845,16 @@
         <v>272</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C239" s="2" t="s">
         <v>212</v>
       </c>
       <c r="D239" s="3" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E239" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F239" s="5">
         <v>27.21</v>
@@ -14880,7 +14894,7 @@
         <v>272</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C240" s="2" t="s">
         <v>212</v>
@@ -14889,7 +14903,7 @@
         <v>41</v>
       </c>
       <c r="E240" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F240" s="5">
         <v>32.57</v>
@@ -14929,7 +14943,7 @@
         <v>272</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C241" s="2" t="s">
         <v>32</v>
@@ -14994,7 +15008,7 @@
         <v>272</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C242" s="2" t="s">
         <v>32</v>
@@ -15059,7 +15073,7 @@
         <v>272</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C243" s="2" t="s">
         <v>32</v>
@@ -15124,13 +15138,13 @@
         <v>272</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C244" s="2" t="s">
         <v>35</v>
       </c>
       <c r="D244" s="3" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E244" s="3" t="s">
         <v>26</v>
@@ -15189,7 +15203,7 @@
         <v>272</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C245" s="2" t="s">
         <v>35</v>
@@ -15254,7 +15268,7 @@
         <v>272</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C246" s="2" t="s">
         <v>35</v>
@@ -15319,7 +15333,7 @@
         <v>272</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C247" s="2" t="s">
         <v>35</v>
@@ -15384,13 +15398,13 @@
         <v>272</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C248" s="2" t="s">
         <v>35</v>
       </c>
       <c r="D248" s="3" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E248" s="3" t="s">
         <v>26</v>
@@ -15449,10 +15463,10 @@
         <v>272</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C249" s="2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D249" s="3" t="s">
         <v>25</v>
@@ -15514,7 +15528,7 @@
         <v>272</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C250" s="2" t="s">
         <v>24</v>
@@ -15579,7 +15593,7 @@
         <v>272</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C251" s="2" t="s">
         <v>48</v>
@@ -15642,13 +15656,13 @@
         <v>272</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C252" s="2" t="s">
         <v>48</v>
       </c>
       <c r="D252" s="3" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E252" s="3" t="s">
         <v>49</v>
@@ -15705,10 +15719,10 @@
         <v>272</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C253" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D253" s="3" t="s">
         <v>25</v>
@@ -15740,7 +15754,7 @@
       <c r="S253" s="3"/>
       <c r="T253" s="3"/>
       <c r="U253" s="2" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="254" spans="1:21" ht="36" x14ac:dyDescent="0.25">
@@ -15748,13 +15762,13 @@
         <v>272</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D254" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E254" s="3" t="s">
         <v>149</v>
@@ -15783,7 +15797,7 @@
       <c r="S254" s="3"/>
       <c r="T254" s="3"/>
       <c r="U254" s="2" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="255" spans="1:21" ht="36" x14ac:dyDescent="0.25">
@@ -15791,13 +15805,13 @@
         <v>272</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D255" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E255" s="3" t="s">
         <v>149</v>
@@ -15826,7 +15840,7 @@
       <c r="S255" s="3"/>
       <c r="T255" s="3"/>
       <c r="U255" s="2" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="256" spans="1:21" ht="27" x14ac:dyDescent="0.25">
@@ -15834,7 +15848,7 @@
         <v>272</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C256" s="2" t="s">
         <v>24</v>
@@ -15899,7 +15913,7 @@
         <v>272</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C257" s="2" t="s">
         <v>24</v>
@@ -15908,7 +15922,7 @@
         <v>25</v>
       </c>
       <c r="E257" s="3" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F257" s="4">
         <v>85.8</v>
@@ -15950,7 +15964,7 @@
       <c r="S257" s="3"/>
       <c r="T257" s="3"/>
       <c r="U257" s="2" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="258" spans="1:21" ht="27" x14ac:dyDescent="0.25">
@@ -15958,7 +15972,7 @@
         <v>272</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C258" s="2" t="s">
         <v>32</v>
@@ -15987,7 +16001,7 @@
       <c r="S258" s="3"/>
       <c r="T258" s="3"/>
       <c r="U258" s="2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="259" spans="1:21" ht="27" x14ac:dyDescent="0.25">
@@ -15995,7 +16009,7 @@
         <v>272</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C259" s="2" t="s">
         <v>32</v>
@@ -16024,7 +16038,7 @@
       <c r="S259" s="3"/>
       <c r="T259" s="3"/>
       <c r="U259" s="2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="260" spans="1:21" ht="27" x14ac:dyDescent="0.25">
@@ -16032,7 +16046,7 @@
         <v>272</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C260" s="2" t="s">
         <v>32</v>
@@ -16061,7 +16075,7 @@
       <c r="S260" s="3"/>
       <c r="T260" s="3"/>
       <c r="U260" s="2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="261" spans="1:21" ht="27" x14ac:dyDescent="0.25">
@@ -16069,13 +16083,13 @@
         <v>272</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C261" s="2" t="s">
         <v>35</v>
       </c>
       <c r="D261" s="3" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E261" s="3" t="s">
         <v>26</v>
@@ -16098,7 +16112,7 @@
       <c r="S261" s="3"/>
       <c r="T261" s="3"/>
       <c r="U261" s="2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="262" spans="1:21" ht="27" x14ac:dyDescent="0.25">
@@ -16106,7 +16120,7 @@
         <v>272</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C262" s="2" t="s">
         <v>35</v>
@@ -16135,7 +16149,7 @@
       <c r="S262" s="3"/>
       <c r="T262" s="3"/>
       <c r="U262" s="2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="263" spans="1:21" ht="27" x14ac:dyDescent="0.25">
@@ -16143,7 +16157,7 @@
         <v>272</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C263" s="2" t="s">
         <v>35</v>
@@ -16172,7 +16186,7 @@
       <c r="S263" s="3"/>
       <c r="T263" s="3"/>
       <c r="U263" s="2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="264" spans="1:21" ht="27" x14ac:dyDescent="0.25">
@@ -16180,7 +16194,7 @@
         <v>272</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C264" s="2" t="s">
         <v>35</v>
@@ -16209,7 +16223,7 @@
       <c r="S264" s="3"/>
       <c r="T264" s="3"/>
       <c r="U264" s="2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="265" spans="1:21" ht="27" x14ac:dyDescent="0.25">
@@ -16217,13 +16231,13 @@
         <v>272</v>
       </c>
       <c r="B265" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C265" s="2" t="s">
         <v>35</v>
       </c>
       <c r="D265" s="3" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E265" s="3" t="s">
         <v>26</v>
@@ -16246,7 +16260,7 @@
       <c r="S265" s="3"/>
       <c r="T265" s="3"/>
       <c r="U265" s="2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="266" spans="1:21" ht="27" x14ac:dyDescent="0.25">
@@ -16254,7 +16268,7 @@
         <v>272</v>
       </c>
       <c r="B266" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C266" s="2" t="s">
         <v>24</v>
@@ -16304,19 +16318,19 @@
     </row>
     <row r="267" spans="1:21" ht="27" x14ac:dyDescent="0.25">
       <c r="A267" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B267" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C267" s="2" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D267" s="3" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="E267" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F267" s="6">
         <v>261314</v>
@@ -16369,19 +16383,19 @@
     </row>
     <row r="268" spans="1:21" ht="27" x14ac:dyDescent="0.25">
       <c r="A268" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B268" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C268" s="2" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D268" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="E268" s="3" t="s">
         <v>320</v>
-      </c>
-      <c r="E268" s="3" t="s">
-        <v>319</v>
       </c>
       <c r="F268" s="6">
         <v>569652</v>
@@ -16434,19 +16448,19 @@
     </row>
     <row r="269" spans="1:21" ht="27" x14ac:dyDescent="0.25">
       <c r="A269" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B269" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C269" s="2" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D269" s="3" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E269" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F269" s="6">
         <v>671</v>
@@ -16499,19 +16513,19 @@
     </row>
     <row r="270" spans="1:21" ht="27" x14ac:dyDescent="0.25">
       <c r="A270" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B270" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C270" s="2" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D270" s="3" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E270" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F270" s="6">
         <v>1397</v>
@@ -16564,19 +16578,19 @@
     </row>
     <row r="271" spans="1:21" ht="27" x14ac:dyDescent="0.25">
       <c r="A271" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B271" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C271" s="2" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D271" s="3" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E271" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F271" s="6">
         <v>4990</v>
@@ -16629,19 +16643,19 @@
     </row>
     <row r="272" spans="1:21" ht="27" x14ac:dyDescent="0.25">
       <c r="A272" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B272" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C272" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D272" s="3" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="E272" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F272" s="6">
         <v>234568</v>
@@ -16694,19 +16708,19 @@
     </row>
     <row r="273" spans="1:21" ht="27" x14ac:dyDescent="0.25">
       <c r="A273" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C273" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D273" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="E273" s="3" t="s">
         <v>320</v>
-      </c>
-      <c r="E273" s="3" t="s">
-        <v>319</v>
       </c>
       <c r="F273" s="6">
         <v>1491253</v>
@@ -16759,19 +16773,19 @@
     </row>
     <row r="274" spans="1:21" ht="27" x14ac:dyDescent="0.25">
       <c r="A274" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B274" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C274" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D274" s="3" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E274" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F274" s="6">
         <v>56208</v>
@@ -16824,19 +16838,19 @@
     </row>
     <row r="275" spans="1:21" ht="27" x14ac:dyDescent="0.25">
       <c r="A275" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B275" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C275" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D275" s="3" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E275" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F275" s="6">
         <v>8362</v>
@@ -16889,19 +16903,19 @@
     </row>
     <row r="276" spans="1:21" ht="27" x14ac:dyDescent="0.25">
       <c r="A276" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B276" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C276" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D276" s="3" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E276" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F276" s="6">
         <v>5141</v>
@@ -16954,19 +16968,19 @@
     </row>
     <row r="277" spans="1:21" ht="27" x14ac:dyDescent="0.25">
       <c r="A277" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B277" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C277" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="D277" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="D277" s="3" t="s">
-        <v>323</v>
-      </c>
       <c r="E277" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F277" s="6">
         <v>41</v>
@@ -17019,10 +17033,10 @@
     </row>
     <row r="278" spans="1:21" ht="27" x14ac:dyDescent="0.25">
       <c r="A278" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C278" s="2" t="s">
         <v>24</v>
@@ -17084,10 +17098,10 @@
     </row>
     <row r="279" spans="1:21" ht="27" x14ac:dyDescent="0.25">
       <c r="A279" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B279" s="2" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C279" s="2" t="s">
         <v>24</v>
@@ -17147,10 +17161,10 @@
     </row>
     <row r="280" spans="1:21" ht="27" x14ac:dyDescent="0.25">
       <c r="A280" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B280" s="2" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C280" s="2" t="s">
         <v>24</v>
@@ -17210,13 +17224,13 @@
     </row>
     <row r="281" spans="1:21" ht="27" x14ac:dyDescent="0.25">
       <c r="A281" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B281" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C281" s="2" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D281" s="3" t="s">
         <v>25</v>
@@ -17268,21 +17282,21 @@
       </c>
       <c r="T281" s="3"/>
       <c r="U281" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="282" spans="1:21" ht="27" x14ac:dyDescent="0.25">
       <c r="A282" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B282" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C282" s="2" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D282" s="3" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="E282" s="3" t="s">
         <v>26</v>
@@ -17331,21 +17345,21 @@
       </c>
       <c r="T282" s="3"/>
       <c r="U282" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="283" spans="1:21" ht="27" x14ac:dyDescent="0.25">
       <c r="A283" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B283" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C283" s="2" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D283" s="3" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="E283" s="3" t="s">
         <v>26</v>
@@ -17394,18 +17408,18 @@
       </c>
       <c r="T283" s="3"/>
       <c r="U283" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="284" spans="1:21" ht="27" x14ac:dyDescent="0.25">
       <c r="A284" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B284" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C284" s="2" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D284" s="3" t="s">
         <v>25</v>
@@ -17457,21 +17471,21 @@
       </c>
       <c r="T284" s="3"/>
       <c r="U284" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="285" spans="1:21" ht="27" x14ac:dyDescent="0.25">
       <c r="A285" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B285" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C285" s="2" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D285" s="3" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="E285" s="3" t="s">
         <v>26</v>
@@ -17520,21 +17534,21 @@
       </c>
       <c r="T285" s="3"/>
       <c r="U285" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="286" spans="1:21" ht="27" x14ac:dyDescent="0.25">
       <c r="A286" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B286" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C286" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="D286" s="3" t="s">
         <v>334</v>
-      </c>
-      <c r="D286" s="3" t="s">
-        <v>333</v>
       </c>
       <c r="E286" s="3" t="s">
         <v>26</v>
@@ -17583,15 +17597,15 @@
       </c>
       <c r="T286" s="3"/>
       <c r="U286" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="287" spans="1:21" ht="27" x14ac:dyDescent="0.25">
       <c r="A287" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B287" s="2" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C287" s="2" t="s">
         <v>24</v>
@@ -17600,7 +17614,7 @@
         <v>25</v>
       </c>
       <c r="E287" s="3" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F287" s="5">
         <v>0.38</v>
@@ -17636,15 +17650,15 @@
       <c r="S287" s="3"/>
       <c r="T287" s="3"/>
       <c r="U287" s="2" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="288" spans="1:21" ht="27" x14ac:dyDescent="0.25">
       <c r="A288" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B288" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C288" s="2" t="s">
         <v>24</v>
@@ -17704,10 +17718,10 @@
     </row>
     <row r="289" spans="1:21" ht="36" x14ac:dyDescent="0.25">
       <c r="A289" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B289" s="2" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C289" s="2" t="s">
         <v>24</v>
@@ -17716,7 +17730,7 @@
         <v>25</v>
       </c>
       <c r="E289" s="3" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F289" s="4">
         <v>1674.9</v>
@@ -17767,10 +17781,10 @@
     </row>
     <row r="290" spans="1:21" ht="27" x14ac:dyDescent="0.25">
       <c r="A290" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B290" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C290" s="2" t="s">
         <v>24</v>
@@ -17826,10 +17840,10 @@
     </row>
     <row r="291" spans="1:21" ht="27" x14ac:dyDescent="0.25">
       <c r="A291" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B291" s="2" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C291" s="2" t="s">
         <v>24</v>
@@ -17881,16 +17895,16 @@
     </row>
     <row r="292" spans="1:21" ht="36" x14ac:dyDescent="0.25">
       <c r="A292" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B292" s="2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C292" s="2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D292" s="3" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="E292" s="3" t="s">
         <v>26</v>
@@ -17934,16 +17948,16 @@
     </row>
     <row r="293" spans="1:21" ht="45" x14ac:dyDescent="0.25">
       <c r="A293" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B293" s="2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C293" s="2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D293" s="3" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E293" s="3" t="s">
         <v>26</v>
@@ -17989,13 +18003,13 @@
     </row>
     <row r="294" spans="1:21" ht="18" x14ac:dyDescent="0.25">
       <c r="A294" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B294" s="2" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C294" s="2" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D294" s="3" t="s">
         <v>25</v>
@@ -18054,16 +18068,16 @@
     </row>
     <row r="295" spans="1:21" ht="54" x14ac:dyDescent="0.25">
       <c r="A295" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B295" s="2" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C295" s="2" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D295" s="3" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="E295" s="3" t="s">
         <v>26</v>
@@ -18119,10 +18133,10 @@
     </row>
     <row r="296" spans="1:21" ht="18" x14ac:dyDescent="0.25">
       <c r="A296" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B296" s="2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C296" s="2" t="s">
         <v>32</v>
@@ -18184,10 +18198,10 @@
     </row>
     <row r="297" spans="1:21" ht="18" x14ac:dyDescent="0.25">
       <c r="A297" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B297" s="2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C297" s="2" t="s">
         <v>32</v>
@@ -18249,10 +18263,10 @@
     </row>
     <row r="298" spans="1:21" ht="18" x14ac:dyDescent="0.25">
       <c r="A298" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B298" s="2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C298" s="2" t="s">
         <v>32</v>
@@ -18314,10 +18328,10 @@
     </row>
     <row r="299" spans="1:21" ht="18" x14ac:dyDescent="0.25">
       <c r="A299" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B299" s="2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C299" s="2" t="s">
         <v>35</v>
@@ -18379,10 +18393,10 @@
     </row>
     <row r="300" spans="1:21" ht="18" x14ac:dyDescent="0.25">
       <c r="A300" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B300" s="2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C300" s="2" t="s">
         <v>35</v>
@@ -18444,10 +18458,10 @@
     </row>
     <row r="301" spans="1:21" ht="18" x14ac:dyDescent="0.25">
       <c r="A301" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B301" s="2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C301" s="2" t="s">
         <v>35</v>
@@ -18509,10 +18523,10 @@
     </row>
     <row r="302" spans="1:21" ht="18" x14ac:dyDescent="0.25">
       <c r="A302" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B302" s="2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C302" s="2" t="s">
         <v>35</v>
@@ -18574,10 +18588,10 @@
     </row>
     <row r="303" spans="1:21" ht="18" x14ac:dyDescent="0.25">
       <c r="A303" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B303" s="2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C303" s="2" t="s">
         <v>35</v>
@@ -18639,10 +18653,10 @@
     </row>
     <row r="304" spans="1:21" ht="18" x14ac:dyDescent="0.25">
       <c r="A304" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B304" s="2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C304" s="2" t="s">
         <v>35</v>
@@ -18704,10 +18718,10 @@
     </row>
     <row r="305" spans="1:21" ht="18" x14ac:dyDescent="0.25">
       <c r="A305" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B305" s="2" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C305" s="2" t="s">
         <v>24</v>
@@ -18745,10 +18759,10 @@
     </row>
     <row r="306" spans="1:21" ht="18" x14ac:dyDescent="0.25">
       <c r="A306" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B306" s="2" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C306" s="2" t="s">
         <v>24</v>
@@ -18808,16 +18822,16 @@
     </row>
     <row r="307" spans="1:21" ht="72" x14ac:dyDescent="0.25">
       <c r="A307" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B307" s="2" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C307" s="2" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D307" s="3" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E307" s="3" t="s">
         <v>26</v>
@@ -18868,21 +18882,21 @@
         <v>20.3</v>
       </c>
       <c r="U307" s="2" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="308" spans="1:21" ht="36" x14ac:dyDescent="0.25">
       <c r="A308" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B308" s="2" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C308" s="2" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D308" s="3" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E308" s="3" t="s">
         <v>26</v>
@@ -18933,21 +18947,21 @@
         <v>-1</v>
       </c>
       <c r="U308" s="2" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="309" spans="1:21" ht="72" x14ac:dyDescent="0.25">
       <c r="A309" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B309" s="2" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C309" s="2" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D309" s="3" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E309" s="3" t="s">
         <v>26</v>
@@ -18998,21 +19012,21 @@
         <v>18.899999999999999</v>
       </c>
       <c r="U309" s="2" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="310" spans="1:21" ht="45" x14ac:dyDescent="0.25">
       <c r="A310" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B310" s="2" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C310" s="2" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D310" s="3" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E310" s="3" t="s">
         <v>26</v>
@@ -19063,21 +19077,21 @@
         <v>4.2</v>
       </c>
       <c r="U310" s="2" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="311" spans="1:21" ht="45" x14ac:dyDescent="0.25">
       <c r="A311" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B311" s="2" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C311" s="2" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D311" s="3" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E311" s="3" t="s">
         <v>26</v>
@@ -19128,21 +19142,21 @@
         <v>1.8</v>
       </c>
       <c r="U311" s="2" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="312" spans="1:21" ht="54" x14ac:dyDescent="0.25">
       <c r="A312" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B312" s="2" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C312" s="2" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D312" s="3" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E312" s="3" t="s">
         <v>26</v>
@@ -19193,21 +19207,21 @@
         <v>57.2</v>
       </c>
       <c r="U312" s="2" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="313" spans="1:21" ht="27" x14ac:dyDescent="0.25">
       <c r="A313" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B313" s="2" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C313" s="2" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D313" s="3" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E313" s="3" t="s">
         <v>26</v>
@@ -19258,21 +19272,21 @@
         <v>1.7</v>
       </c>
       <c r="U313" s="2" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="314" spans="1:21" ht="27" x14ac:dyDescent="0.25">
       <c r="A314" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B314" s="2" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C314" s="2" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D314" s="3" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E314" s="3" t="s">
         <v>26</v>
@@ -19323,21 +19337,21 @@
         <v>14.7</v>
       </c>
       <c r="U314" s="2" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="315" spans="1:21" ht="54" x14ac:dyDescent="0.25">
       <c r="A315" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B315" s="2" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C315" s="2" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D315" s="3" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E315" s="3" t="s">
         <v>26</v>
@@ -19388,21 +19402,21 @@
         <v>72.099999999999994</v>
       </c>
       <c r="U315" s="2" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="316" spans="1:21" ht="54" x14ac:dyDescent="0.25">
       <c r="A316" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B316" s="2" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C316" s="2" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D316" s="3" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="E316" s="3" t="s">
         <v>26</v>
@@ -19453,21 +19467,21 @@
         <v>49.8</v>
       </c>
       <c r="U316" s="2" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="317" spans="1:21" ht="36" x14ac:dyDescent="0.25">
       <c r="A317" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B317" s="2" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C317" s="2" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D317" s="3" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E317" s="3" t="s">
         <v>26</v>
@@ -19518,21 +19532,21 @@
         <v>28</v>
       </c>
       <c r="U317" s="2" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="318" spans="1:21" ht="45" x14ac:dyDescent="0.25">
       <c r="A318" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B318" s="2" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C318" s="2" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D318" s="3" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E318" s="3" t="s">
         <v>26</v>
@@ -19583,15 +19597,15 @@
         <v>48</v>
       </c>
       <c r="U318" s="2" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="319" spans="1:21" ht="27" x14ac:dyDescent="0.25">
       <c r="A319" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B319" s="2" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C319" s="2" t="s">
         <v>24</v>
@@ -19648,21 +19662,21 @@
         <v>4.04</v>
       </c>
       <c r="U319" s="2" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="320" spans="1:21" ht="36" x14ac:dyDescent="0.25">
       <c r="A320" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B320" s="2" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C320" s="2" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D320" s="3" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="E320" s="3" t="s">
         <v>94</v>
@@ -19713,21 +19727,21 @@
         <v>1840.15</v>
       </c>
       <c r="U320" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="321" spans="1:21" ht="36" x14ac:dyDescent="0.25">
       <c r="A321" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B321" s="2" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C321" s="2" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D321" s="3" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E321" s="3" t="s">
         <v>94</v>
@@ -19778,21 +19792,21 @@
         <v>705.25</v>
       </c>
       <c r="U321" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="322" spans="1:21" ht="63" x14ac:dyDescent="0.25">
       <c r="A322" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B322" s="2" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C322" s="2" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D322" s="3" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="E322" s="3" t="s">
         <v>94</v>
@@ -19843,21 +19857,21 @@
         <v>12.96</v>
       </c>
       <c r="U322" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="323" spans="1:21" ht="63" x14ac:dyDescent="0.25">
       <c r="A323" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B323" s="2" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C323" s="2" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D323" s="3" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E323" s="3" t="s">
         <v>94</v>
@@ -19908,21 +19922,21 @@
         <v>1.79</v>
       </c>
       <c r="U323" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="324" spans="1:21" ht="63" x14ac:dyDescent="0.25">
       <c r="A324" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B324" s="2" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C324" s="2" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D324" s="3" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="E324" s="3" t="s">
         <v>94</v>
@@ -19973,21 +19987,21 @@
         <v>199.97</v>
       </c>
       <c r="U324" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="325" spans="1:21" ht="72" x14ac:dyDescent="0.25">
       <c r="A325" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B325" s="2" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C325" s="2" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D325" s="3" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E325" s="3" t="s">
         <v>94</v>
@@ -20038,21 +20052,21 @@
         <v>87.2</v>
       </c>
       <c r="U325" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="326" spans="1:21" ht="36" x14ac:dyDescent="0.25">
       <c r="A326" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B326" s="2" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C326" s="2" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D326" s="3" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E326" s="3" t="s">
         <v>94</v>
@@ -20103,21 +20117,21 @@
         <v>3699.5</v>
       </c>
       <c r="U326" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="327" spans="1:21" ht="72" x14ac:dyDescent="0.25">
       <c r="A327" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B327" s="2" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C327" s="2" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D327" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="E327" s="3" t="s">
         <v>94</v>
@@ -20168,21 +20182,21 @@
         <v>3.2</v>
       </c>
       <c r="U327" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="328" spans="1:21" ht="63" x14ac:dyDescent="0.25">
       <c r="A328" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B328" s="2" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C328" s="2" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D328" s="3" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E328" s="3" t="s">
         <v>94</v>
@@ -20233,21 +20247,21 @@
         <v>0</v>
       </c>
       <c r="U328" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="329" spans="1:21" ht="72" x14ac:dyDescent="0.25">
       <c r="A329" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B329" s="2" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C329" s="2" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D329" s="3" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E329" s="3" t="s">
         <v>94</v>
@@ -20298,21 +20312,21 @@
         <v>338.9</v>
       </c>
       <c r="U329" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="330" spans="1:21" ht="81" x14ac:dyDescent="0.25">
       <c r="A330" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B330" s="2" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C330" s="2" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D330" s="3" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E330" s="3" t="s">
         <v>94</v>
@@ -20363,15 +20377,15 @@
         <v>405.8</v>
       </c>
       <c r="U330" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="331" spans="1:21" ht="36" x14ac:dyDescent="0.25">
       <c r="A331" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B331" s="2" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C331" s="2" t="s">
         <v>29</v>
@@ -20427,10 +20441,10 @@
     </row>
     <row r="332" spans="1:21" ht="36" x14ac:dyDescent="0.25">
       <c r="A332" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B332" s="2" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C332" s="2" t="s">
         <v>29</v>
@@ -20486,10 +20500,10 @@
     </row>
     <row r="333" spans="1:21" ht="36" x14ac:dyDescent="0.25">
       <c r="A333" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B333" s="2" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C333" s="2" t="s">
         <v>29</v>
@@ -20545,10 +20559,10 @@
     </row>
     <row r="334" spans="1:21" ht="36" x14ac:dyDescent="0.25">
       <c r="A334" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B334" s="2" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C334" s="2" t="s">
         <v>48</v>
@@ -20605,15 +20619,15 @@
         <v>2.73</v>
       </c>
       <c r="U334" s="2" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="335" spans="1:21" ht="36" x14ac:dyDescent="0.25">
       <c r="A335" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B335" s="2" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C335" s="2" t="s">
         <v>48</v>
@@ -20670,21 +20684,21 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="U335" s="2" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="336" spans="1:21" ht="27" x14ac:dyDescent="0.25">
       <c r="A336" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B336" s="2" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C336" s="2" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D336" s="3" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E336" s="3" t="s">
         <v>26</v>
@@ -20740,16 +20754,16 @@
     </row>
     <row r="337" spans="1:21" ht="27" x14ac:dyDescent="0.25">
       <c r="A337" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B337" s="2" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C337" s="2" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D337" s="3" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E337" s="3" t="s">
         <v>26</v>
@@ -20805,16 +20819,16 @@
     </row>
     <row r="338" spans="1:21" ht="27" x14ac:dyDescent="0.25">
       <c r="A338" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B338" s="2" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C338" s="2" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D338" s="3" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E338" s="3" t="s">
         <v>26</v>
@@ -20870,16 +20884,16 @@
     </row>
     <row r="339" spans="1:21" ht="27" x14ac:dyDescent="0.25">
       <c r="A339" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B339" s="2" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C339" s="2" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D339" s="3" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="E339" s="3" t="s">
         <v>26</v>
@@ -20935,19 +20949,19 @@
     </row>
     <row r="340" spans="1:21" ht="18" x14ac:dyDescent="0.25">
       <c r="A340" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B340" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C340" s="2" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D340" s="3" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="E340" s="3" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="F340" s="4">
         <v>27.7</v>
@@ -21000,19 +21014,19 @@
     </row>
     <row r="341" spans="1:21" ht="18" x14ac:dyDescent="0.25">
       <c r="A341" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B341" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C341" s="2" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D341" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="E341" s="3" t="s">
         <v>400</v>
-      </c>
-      <c r="E341" s="3" t="s">
-        <v>399</v>
       </c>
       <c r="F341" s="4">
         <v>29.6</v>
@@ -21065,19 +21079,19 @@
     </row>
     <row r="342" spans="1:21" ht="18" x14ac:dyDescent="0.25">
       <c r="A342" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B342" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C342" s="2" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D342" s="3" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E342" s="3" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="F342" s="4">
         <v>50.5</v>
@@ -21130,19 +21144,19 @@
     </row>
     <row r="343" spans="1:21" ht="18" x14ac:dyDescent="0.25">
       <c r="A343" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B343" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C343" s="2" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D343" s="3" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="E343" s="3" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="F343" s="4">
         <v>65.8</v>
@@ -21195,19 +21209,19 @@
     </row>
     <row r="344" spans="1:21" ht="18" x14ac:dyDescent="0.25">
       <c r="A344" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B344" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C344" s="2" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D344" s="3" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="E344" s="3" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="F344" s="4">
         <v>57.7</v>
@@ -21260,19 +21274,19 @@
     </row>
     <row r="345" spans="1:21" ht="18" x14ac:dyDescent="0.25">
       <c r="A345" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B345" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C345" s="2" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D345" s="3" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E345" s="3" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="F345" s="4">
         <v>31.2</v>
@@ -21325,19 +21339,19 @@
     </row>
     <row r="346" spans="1:21" ht="18" x14ac:dyDescent="0.25">
       <c r="A346" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B346" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C346" s="2" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D346" s="3" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E346" s="3" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="F346" s="4">
         <v>25.4</v>
@@ -21390,19 +21404,19 @@
     </row>
     <row r="347" spans="1:21" ht="27" x14ac:dyDescent="0.25">
       <c r="A347" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B347" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C347" s="2" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D347" s="3" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="E347" s="3" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="F347" s="4">
         <v>38</v>
@@ -21455,19 +21469,19 @@
     </row>
     <row r="348" spans="1:21" ht="18" x14ac:dyDescent="0.25">
       <c r="A348" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B348" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C348" s="2" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D348" s="3" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="E348" s="3" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="F348" s="4">
         <v>54.9</v>
@@ -21520,19 +21534,19 @@
     </row>
     <row r="349" spans="1:21" ht="18" x14ac:dyDescent="0.25">
       <c r="A349" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B349" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C349" s="2" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D349" s="3" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="E349" s="3" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="F349" s="4">
         <v>23.7</v>
@@ -21585,19 +21599,19 @@
     </row>
     <row r="350" spans="1:21" ht="18" x14ac:dyDescent="0.25">
       <c r="A350" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B350" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C350" s="2" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D350" s="3" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="E350" s="3" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="F350" s="4">
         <v>27.7</v>
@@ -21650,19 +21664,19 @@
     </row>
     <row r="351" spans="1:21" ht="18" x14ac:dyDescent="0.25">
       <c r="A351" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B351" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C351" s="2" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D351" s="3" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E351" s="3" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="F351" s="4">
         <v>42.5</v>
@@ -21715,19 +21729,19 @@
     </row>
     <row r="352" spans="1:21" ht="18" x14ac:dyDescent="0.25">
       <c r="A352" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B352" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C352" s="2" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D352" s="3" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="E352" s="3" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="F352" s="4">
         <v>50.9</v>
@@ -21780,19 +21794,19 @@
     </row>
     <row r="353" spans="1:21" ht="18" x14ac:dyDescent="0.25">
       <c r="A353" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B353" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C353" s="2" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D353" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="E353" s="3" t="s">
         <v>400</v>
-      </c>
-      <c r="E353" s="3" t="s">
-        <v>399</v>
       </c>
       <c r="F353" s="4">
         <v>25.1</v>
@@ -21845,19 +21859,19 @@
     </row>
     <row r="354" spans="1:21" ht="18" x14ac:dyDescent="0.25">
       <c r="A354" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B354" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C354" s="2" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D354" s="3" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E354" s="3" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="F354" s="4">
         <v>26.2</v>
@@ -21910,19 +21924,19 @@
     </row>
     <row r="355" spans="1:21" ht="18" x14ac:dyDescent="0.25">
       <c r="A355" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B355" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C355" s="2" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D355" s="3" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="E355" s="3" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="F355" s="3"/>
       <c r="G355" s="4">
@@ -21973,19 +21987,19 @@
     </row>
     <row r="356" spans="1:21" ht="18" x14ac:dyDescent="0.25">
       <c r="A356" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B356" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C356" s="2" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D356" s="3" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="E356" s="3" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="F356" s="4">
         <v>44.3</v>
@@ -22038,19 +22052,19 @@
     </row>
     <row r="357" spans="1:21" ht="18" x14ac:dyDescent="0.25">
       <c r="A357" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B357" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C357" s="2" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D357" s="3" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E357" s="3" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="F357" s="4">
         <v>19.3</v>
@@ -22103,19 +22117,19 @@
     </row>
     <row r="358" spans="1:21" ht="18" x14ac:dyDescent="0.25">
       <c r="A358" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B358" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C358" s="2" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D358" s="3" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E358" s="3" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="F358" s="4">
         <v>20.3</v>
@@ -22168,19 +22182,19 @@
     </row>
     <row r="359" spans="1:21" ht="27" x14ac:dyDescent="0.25">
       <c r="A359" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B359" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C359" s="2" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D359" s="3" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="E359" s="3" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="F359" s="4">
         <v>30.9</v>
@@ -22233,19 +22247,19 @@
     </row>
     <row r="360" spans="1:21" ht="18" x14ac:dyDescent="0.25">
       <c r="A360" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B360" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C360" s="2" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D360" s="3" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="E360" s="3" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="F360" s="4">
         <v>34.799999999999997</v>
@@ -22298,19 +22312,19 @@
     </row>
     <row r="361" spans="1:21" ht="18" x14ac:dyDescent="0.25">
       <c r="A361" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B361" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C361" s="2" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D361" s="3" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="E361" s="3" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="F361" s="3"/>
       <c r="G361" s="4">
@@ -22361,19 +22375,19 @@
     </row>
     <row r="362" spans="1:21" ht="18" x14ac:dyDescent="0.25">
       <c r="A362" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B362" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C362" s="2" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D362" s="3" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="E362" s="3" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="F362" s="3"/>
       <c r="G362" s="4">
@@ -22424,19 +22438,19 @@
     </row>
     <row r="363" spans="1:21" ht="18" x14ac:dyDescent="0.25">
       <c r="A363" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B363" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C363" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="D363" s="3" t="s">
         <v>411</v>
       </c>
-      <c r="D363" s="3" t="s">
-        <v>410</v>
-      </c>
       <c r="E363" s="3" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="F363" s="3"/>
       <c r="G363" s="4">
@@ -22487,13 +22501,13 @@
     </row>
     <row r="364" spans="1:21" ht="36" x14ac:dyDescent="0.25">
       <c r="A364" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B364" s="2" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C364" s="2" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D364" s="3" t="s">
         <v>25</v>
@@ -22547,21 +22561,21 @@
         <v>98.72</v>
       </c>
       <c r="U364" s="2" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="365" spans="1:21" ht="36" x14ac:dyDescent="0.25">
       <c r="A365" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B365" s="2" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C365" s="2" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D365" s="3" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E365" s="3" t="s">
         <v>26</v>
@@ -22612,21 +22626,21 @@
         <v>100</v>
       </c>
       <c r="U365" s="2" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="366" spans="1:21" ht="36" x14ac:dyDescent="0.25">
       <c r="A366" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B366" s="2" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C366" s="2" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D366" s="3" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="E366" s="3" t="s">
         <v>26</v>
@@ -22677,21 +22691,21 @@
         <v>96.13</v>
       </c>
       <c r="U366" s="2" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="367" spans="1:21" ht="36" x14ac:dyDescent="0.25">
       <c r="A367" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B367" s="2" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C367" s="2" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D367" s="3" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="E367" s="3" t="s">
         <v>26</v>
@@ -22742,18 +22756,18 @@
         <v>99.18</v>
       </c>
       <c r="U367" s="2" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="368" spans="1:21" ht="27" x14ac:dyDescent="0.25">
       <c r="A368" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B368" s="2" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C368" s="2" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="D368" s="3" t="s">
         <v>25</v>
@@ -22807,21 +22821,21 @@
         <v>99.8</v>
       </c>
       <c r="U368" s="2" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="369" spans="1:21" ht="27" x14ac:dyDescent="0.25">
       <c r="A369" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B369" s="2" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C369" s="2" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="D369" s="3" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E369" s="3" t="s">
         <v>26</v>
@@ -22872,21 +22886,21 @@
         <v>99.8</v>
       </c>
       <c r="U369" s="2" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="370" spans="1:21" ht="27" x14ac:dyDescent="0.25">
       <c r="A370" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B370" s="2" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C370" s="2" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="D370" s="3" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="E370" s="3" t="s">
         <v>26</v>
@@ -22937,21 +22951,21 @@
         <v>99.8</v>
       </c>
       <c r="U370" s="2" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="371" spans="1:21" ht="27" x14ac:dyDescent="0.25">
       <c r="A371" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B371" s="2" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C371" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="D371" s="3" t="s">
         <v>418</v>
-      </c>
-      <c r="D371" s="3" t="s">
-        <v>417</v>
       </c>
       <c r="E371" s="3" t="s">
         <v>26</v>
@@ -23002,15 +23016,15 @@
         <v>99.6</v>
       </c>
       <c r="U371" s="2" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="372" spans="1:21" ht="36" x14ac:dyDescent="0.25">
       <c r="A372" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B372" s="2" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C372" s="2" t="s">
         <v>53</v>
@@ -23062,10 +23076,10 @@
     </row>
     <row r="373" spans="1:21" ht="63" x14ac:dyDescent="0.25">
       <c r="A373" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B373" s="2" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C373" s="2" t="s">
         <v>53</v>
@@ -23117,10 +23131,10 @@
     </row>
     <row r="374" spans="1:21" ht="27" x14ac:dyDescent="0.25">
       <c r="A374" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B374" s="2" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C374" s="2" t="s">
         <v>24</v>
@@ -23172,10 +23186,10 @@
     </row>
     <row r="375" spans="1:21" ht="27" x14ac:dyDescent="0.25">
       <c r="A375" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B375" s="2" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C375" s="2" t="s">
         <v>24</v>
@@ -23227,10 +23241,10 @@
     </row>
     <row r="376" spans="1:21" ht="36" x14ac:dyDescent="0.25">
       <c r="A376" s="2" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B376" s="2" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C376" s="2" t="s">
         <v>24</v>
@@ -23292,19 +23306,19 @@
     </row>
     <row r="377" spans="1:21" ht="36" x14ac:dyDescent="0.25">
       <c r="A377" s="2" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B377" s="2" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C377" s="2" t="s">
         <v>24</v>
       </c>
       <c r="D377" s="3" t="s">
-        <v>25</v>
+        <v>279</v>
       </c>
       <c r="E377" s="3" t="s">
-        <v>424</v>
+        <v>280</v>
       </c>
       <c r="F377" s="4">
         <v>627714.30000000005</v>
@@ -23357,19 +23371,19 @@
     </row>
     <row r="378" spans="1:21" ht="36" x14ac:dyDescent="0.25">
       <c r="A378" s="2" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B378" s="2" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C378" s="2" t="s">
         <v>24</v>
       </c>
       <c r="D378" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="E378" s="3" t="s">
         <v>280</v>
-      </c>
-      <c r="E378" s="3" t="s">
-        <v>424</v>
       </c>
       <c r="F378" s="5">
         <v>16.5</v>
@@ -23422,7 +23436,7 @@
     </row>
     <row r="379" spans="1:21" ht="45" x14ac:dyDescent="0.25">
       <c r="A379" s="2" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B379" s="2" t="s">
         <v>425</v>
@@ -23487,7 +23501,7 @@
     </row>
     <row r="380" spans="1:21" ht="36" x14ac:dyDescent="0.25">
       <c r="A380" s="2" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B380" s="2" t="s">
         <v>427</v>
@@ -23536,7 +23550,7 @@
     </row>
     <row r="381" spans="1:21" ht="36" x14ac:dyDescent="0.25">
       <c r="A381" s="2" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B381" s="2" t="s">
         <v>427</v>
@@ -23583,7 +23597,7 @@
     </row>
     <row r="382" spans="1:21" ht="36" x14ac:dyDescent="0.25">
       <c r="A382" s="2" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B382" s="2" t="s">
         <v>427</v>
@@ -23630,7 +23644,7 @@
     </row>
     <row r="383" spans="1:21" ht="36" x14ac:dyDescent="0.25">
       <c r="A383" s="2" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B383" s="2" t="s">
         <v>433</v>
@@ -23689,7 +23703,7 @@
     </row>
     <row r="384" spans="1:21" ht="36" x14ac:dyDescent="0.25">
       <c r="A384" s="2" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B384" s="2" t="s">
         <v>434</v>
@@ -23740,7 +23754,7 @@
     </row>
     <row r="385" spans="1:21" ht="36" x14ac:dyDescent="0.25">
       <c r="A385" s="2" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B385" s="2" t="s">
         <v>436</v>
@@ -23805,7 +23819,7 @@
     </row>
     <row r="386" spans="1:21" ht="36" x14ac:dyDescent="0.25">
       <c r="A386" s="2" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B386" s="2" t="s">
         <v>438</v>
@@ -23930,7 +23944,7 @@
         <v>2.73</v>
       </c>
       <c r="U387" s="2" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="388" spans="1:21" ht="36" x14ac:dyDescent="0.25">
@@ -23995,7 +24009,7 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="U388" s="2" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="389" spans="1:21" ht="36" x14ac:dyDescent="0.25">
@@ -25408,7 +25422,7 @@
         <v>24104</v>
       </c>
       <c r="U413" s="2" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="414" spans="1:21" ht="27" x14ac:dyDescent="0.25">
@@ -25656,7 +25670,7 @@
         <v>24104</v>
       </c>
       <c r="U417" s="2" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="418" spans="1:21" ht="27" x14ac:dyDescent="0.25">
@@ -27485,7 +27499,7 @@
         <v>17.100000000000001</v>
       </c>
       <c r="U452" s="2" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="453" spans="1:21" ht="18" x14ac:dyDescent="0.25">
@@ -27550,7 +27564,7 @@
         <v>89.2</v>
       </c>
       <c r="U453" s="2" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="454" spans="1:21" ht="18" x14ac:dyDescent="0.25">
@@ -27810,7 +27824,7 @@
         <v>1</v>
       </c>
       <c r="U457" s="2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="458" spans="1:21" ht="18" x14ac:dyDescent="0.25">
@@ -28265,7 +28279,7 @@
         <v>1.4</v>
       </c>
       <c r="U464" s="2" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="465" spans="1:21" ht="27" x14ac:dyDescent="0.25">
@@ -28282,7 +28296,7 @@
         <v>536</v>
       </c>
       <c r="E465" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F465" s="6">
         <v>37896</v>
@@ -28347,7 +28361,7 @@
         <v>537</v>
       </c>
       <c r="E466" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F466" s="4">
         <v>103.2</v>
@@ -28412,7 +28426,7 @@
         <v>538</v>
       </c>
       <c r="E467" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F467" s="4">
         <v>102.6</v>
@@ -28477,7 +28491,7 @@
         <v>539</v>
       </c>
       <c r="E468" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F468" s="4">
         <v>19.600000000000001</v>
@@ -28542,7 +28556,7 @@
         <v>540</v>
       </c>
       <c r="E469" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F469" s="4">
         <v>53.7</v>
@@ -28607,7 +28621,7 @@
         <v>541</v>
       </c>
       <c r="E470" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F470" s="4">
         <v>-7.4</v>
@@ -29085,7 +29099,7 @@
     <hyperlink ref="A2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.39370078740157499" right="0.39370078740157499" top="0.39370078740157499" bottom="0.39370078740157499" header="0.39370078740157499" footer="0.39370078740157499"/>
-  <pageSetup paperSize="9" scale="71" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" scale="70" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
   <headerFooter alignWithMargins="0"/>
   <drawing r:id="rId3"/>
 </worksheet>

--- a/assets/excel/pl/wskazniki_globalne.xlsx
+++ b/assets/excel/pl/wskazniki_globalne.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dregerj\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88B5E940-2C4F-4191-BC10-C343FC43749D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12E247FD-E678-4EE9-A83F-63B6E302089B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1929,8 +1929,8 @@
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>1294790</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>457200</xdr:rowOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1950,6 +1950,10 @@
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2190140" cy="457200"/>
+        </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
@@ -11791,7 +11795,7 @@
         <v>29.8</v>
       </c>
       <c r="P174" s="4">
-        <v>32.6</v>
+        <v>30.1</v>
       </c>
       <c r="Q174" s="4">
         <v>30.4</v>

--- a/assets/excel/pl/wskazniki_globalne.xlsx
+++ b/assets/excel/pl/wskazniki_globalne.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dregerj\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\niewiadomskaew\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12E247FD-E678-4EE9-A83F-63B6E302089B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E29897ED-07EE-4839-AADA-60A27D731FFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1693,7 +1693,7 @@
     <t>100% rejestracja zgonów</t>
   </si>
   <si>
-    <t>Ostatnia aktualizacja: 21-04-2026, 11:39</t>
+    <t>Ostatnia aktualizacja: 28-04-2026, 10:52</t>
   </si>
 </sst>
 </file>
@@ -1929,8 +1929,8 @@
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>1294790</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>457200</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1950,10 +1950,6 @@
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="2190140" cy="457200"/>
-        </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
@@ -3968,7 +3964,9 @@
       <c r="S29" s="4">
         <v>58.7</v>
       </c>
-      <c r="T29" s="3"/>
+      <c r="T29" s="4">
+        <v>60.8</v>
+      </c>
       <c r="U29" s="3"/>
       <c r="V29" s="2" t="s">
         <v>28</v>
@@ -4032,7 +4030,9 @@
       <c r="S30" s="4">
         <v>12.2</v>
       </c>
-      <c r="T30" s="3"/>
+      <c r="T30" s="4">
+        <v>12.4</v>
+      </c>
       <c r="U30" s="3"/>
       <c r="V30" s="2" t="s">
         <v>28</v>
@@ -4096,7 +4096,9 @@
       <c r="S31" s="4">
         <v>10.5</v>
       </c>
-      <c r="T31" s="3"/>
+      <c r="T31" s="4">
+        <v>11.4</v>
+      </c>
       <c r="U31" s="3"/>
       <c r="V31" s="2" t="s">
         <v>28</v>
@@ -4160,7 +4162,9 @@
       <c r="S32" s="4">
         <v>36</v>
       </c>
-      <c r="T32" s="3"/>
+      <c r="T32" s="4">
+        <v>37</v>
+      </c>
       <c r="U32" s="3"/>
       <c r="V32" s="2" t="s">
         <v>28</v>
@@ -5238,8 +5242,12 @@
       <c r="S50" s="5">
         <v>0.9</v>
       </c>
-      <c r="T50" s="3"/>
-      <c r="U50" s="3"/>
+      <c r="T50" s="5">
+        <v>1.23</v>
+      </c>
+      <c r="U50" s="5">
+        <v>0.8</v>
+      </c>
       <c r="V50" s="2" t="s">
         <v>96</v>
       </c>
@@ -7819,7 +7827,9 @@
       <c r="T91" s="5">
         <v>6.03</v>
       </c>
-      <c r="U91" s="3"/>
+      <c r="U91" s="5">
+        <v>0.22</v>
+      </c>
       <c r="V91" s="2" t="s">
         <v>96</v>
       </c>
@@ -10667,7 +10677,9 @@
       <c r="T150" s="5">
         <v>9.7899999999999991</v>
       </c>
-      <c r="U150" s="3"/>
+      <c r="U150" s="5">
+        <v>9.67</v>
+      </c>
       <c r="V150" s="2" t="s">
         <v>96</v>
       </c>
@@ -13555,7 +13567,9 @@
       <c r="T208" s="5">
         <v>0.69</v>
       </c>
-      <c r="U208" s="3"/>
+      <c r="U208" s="5">
+        <v>1.8</v>
+      </c>
       <c r="V208" s="2" t="s">
         <v>96</v>
       </c>
@@ -13851,7 +13865,9 @@
       <c r="T213" s="5">
         <v>8.32</v>
       </c>
-      <c r="U213" s="3"/>
+      <c r="U213" s="5">
+        <v>3.5</v>
+      </c>
       <c r="V213" s="2" t="s">
         <v>96</v>
       </c>
@@ -13915,9 +13931,11 @@
         <v>0.6</v>
       </c>
       <c r="T214" s="4">
-        <v>3.3</v>
-      </c>
-      <c r="U214" s="3"/>
+        <v>3.5</v>
+      </c>
+      <c r="U214" s="4">
+        <v>4</v>
+      </c>
       <c r="V214" s="2" t="s">
         <v>28</v>
       </c>
@@ -13978,12 +13996,14 @@
         <v>9.6</v>
       </c>
       <c r="S215" s="4">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="T215" s="4">
-        <v>14</v>
-      </c>
-      <c r="U215" s="3"/>
+        <v>14.1</v>
+      </c>
+      <c r="U215" s="4">
+        <v>7.8</v>
+      </c>
       <c r="V215" s="2" t="s">
         <v>28</v>
       </c>
@@ -15367,7 +15387,9 @@
       <c r="T241" s="4">
         <v>2.9</v>
       </c>
-      <c r="U241" s="3"/>
+      <c r="U241" s="4">
+        <v>3.1</v>
+      </c>
       <c r="V241" s="2" t="s">
         <v>28</v>
       </c>
@@ -15433,7 +15455,9 @@
       <c r="T242" s="4">
         <v>2.7</v>
       </c>
-      <c r="U242" s="3"/>
+      <c r="U242" s="4">
+        <v>2.9</v>
+      </c>
       <c r="V242" s="2" t="s">
         <v>28</v>
       </c>
@@ -15499,7 +15523,9 @@
       <c r="T243" s="4">
         <v>3.1</v>
       </c>
-      <c r="U243" s="3"/>
+      <c r="U243" s="4">
+        <v>3.4</v>
+      </c>
       <c r="V243" s="2" t="s">
         <v>28</v>
       </c>
@@ -15565,7 +15591,9 @@
       <c r="T244" s="4">
         <v>10.9</v>
       </c>
-      <c r="U244" s="3"/>
+      <c r="U244" s="4">
+        <v>12.2</v>
+      </c>
       <c r="V244" s="2" t="s">
         <v>28</v>
       </c>
@@ -15631,7 +15659,9 @@
       <c r="T245" s="4">
         <v>3.4</v>
       </c>
-      <c r="U245" s="3"/>
+      <c r="U245" s="4">
+        <v>3.6</v>
+      </c>
       <c r="V245" s="2" t="s">
         <v>28</v>
       </c>
@@ -15697,7 +15727,9 @@
       <c r="T246" s="4">
         <v>2.2000000000000002</v>
       </c>
-      <c r="U246" s="3"/>
+      <c r="U246" s="4">
+        <v>2.2999999999999998</v>
+      </c>
       <c r="V246" s="2" t="s">
         <v>28</v>
       </c>
@@ -15763,7 +15795,9 @@
       <c r="T247" s="4">
         <v>1.9</v>
       </c>
-      <c r="U247" s="3"/>
+      <c r="U247" s="4">
+        <v>2.2999999999999998</v>
+      </c>
       <c r="V247" s="2" t="s">
         <v>28</v>
       </c>
@@ -15829,7 +15863,9 @@
       <c r="T248" s="4">
         <v>1.9</v>
       </c>
-      <c r="U248" s="3"/>
+      <c r="U248" s="4">
+        <v>1.9</v>
+      </c>
       <c r="V248" s="2" t="s">
         <v>28</v>
       </c>
@@ -15895,7 +15931,9 @@
       <c r="T249" s="4">
         <v>4.4000000000000004</v>
       </c>
-      <c r="U249" s="3"/>
+      <c r="U249" s="4">
+        <v>7.4</v>
+      </c>
       <c r="V249" s="2" t="s">
         <v>28</v>
       </c>
@@ -15961,7 +15999,9 @@
       <c r="T250" s="4">
         <v>7</v>
       </c>
-      <c r="U250" s="3"/>
+      <c r="U250" s="4">
+        <v>7.1</v>
+      </c>
       <c r="V250" s="2" t="s">
         <v>28</v>
       </c>
@@ -16303,7 +16343,7 @@
         <v>0.03</v>
       </c>
       <c r="T256" s="5">
-        <v>0.1</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="U256" s="3"/>
       <c r="V256" s="2" t="s">
@@ -17513,9 +17553,11 @@
         <v>17.5</v>
       </c>
       <c r="T278" s="4">
-        <v>16.100000000000001</v>
-      </c>
-      <c r="U278" s="3"/>
+        <v>15.4</v>
+      </c>
+      <c r="U278" s="4">
+        <v>14.4</v>
+      </c>
       <c r="V278" s="2" t="s">
         <v>28</v>
       </c>
@@ -18287,7 +18329,9 @@
       <c r="T290" s="5">
         <v>46.56</v>
       </c>
-      <c r="U290" s="3"/>
+      <c r="U290" s="5">
+        <v>45.05</v>
+      </c>
       <c r="V290" s="2" t="s">
         <v>96</v>
       </c>
@@ -20209,7 +20253,9 @@
       <c r="T320" s="5">
         <v>1840.15</v>
       </c>
-      <c r="U320" s="3"/>
+      <c r="U320" s="5">
+        <v>1635.99</v>
+      </c>
       <c r="V320" s="2" t="s">
         <v>376</v>
       </c>
@@ -20275,7 +20321,9 @@
       <c r="T321" s="5">
         <v>705.25</v>
       </c>
-      <c r="U321" s="3"/>
+      <c r="U321" s="5">
+        <v>530</v>
+      </c>
       <c r="V321" s="2" t="s">
         <v>376</v>
       </c>
@@ -20341,7 +20389,9 @@
       <c r="T322" s="5">
         <v>12.96</v>
       </c>
-      <c r="U322" s="3"/>
+      <c r="U322" s="5">
+        <v>11.41</v>
+      </c>
       <c r="V322" s="2" t="s">
         <v>376</v>
       </c>
@@ -20407,7 +20457,9 @@
       <c r="T323" s="5">
         <v>1.79</v>
       </c>
-      <c r="U323" s="3"/>
+      <c r="U323" s="5">
+        <v>2.73</v>
+      </c>
       <c r="V323" s="2" t="s">
         <v>376</v>
       </c>
@@ -20473,7 +20525,9 @@
       <c r="T324" s="5">
         <v>199.97</v>
       </c>
-      <c r="U324" s="3"/>
+      <c r="U324" s="5">
+        <v>200.12</v>
+      </c>
       <c r="V324" s="2" t="s">
         <v>376</v>
       </c>
@@ -20539,7 +20593,9 @@
       <c r="T325" s="5">
         <v>87.2</v>
       </c>
-      <c r="U325" s="3"/>
+      <c r="U325" s="5">
+        <v>88.02</v>
+      </c>
       <c r="V325" s="2" t="s">
         <v>376</v>
       </c>
@@ -25039,7 +25095,9 @@
       <c r="T396" s="5">
         <v>8.32</v>
       </c>
-      <c r="U396" s="3"/>
+      <c r="U396" s="5">
+        <v>3.5</v>
+      </c>
       <c r="V396" s="2" t="s">
         <v>96</v>
       </c>
@@ -26133,7 +26191,9 @@
       <c r="T415" s="5">
         <v>1.93</v>
       </c>
-      <c r="U415" s="3"/>
+      <c r="U415" s="5">
+        <v>0.1</v>
+      </c>
       <c r="V415" s="2" t="s">
         <v>96</v>
       </c>
@@ -26193,7 +26253,9 @@
       <c r="T416" s="5">
         <v>1.93</v>
       </c>
-      <c r="U416" s="3"/>
+      <c r="U416" s="5">
+        <v>0.1</v>
+      </c>
       <c r="V416" s="2" t="s">
         <v>96</v>
       </c>
@@ -26498,7 +26560,9 @@
       <c r="S421" s="5">
         <v>0.05</v>
       </c>
-      <c r="T421" s="3"/>
+      <c r="T421" s="5">
+        <v>0.03</v>
+      </c>
       <c r="U421" s="3"/>
       <c r="V421" s="2" t="s">
         <v>488</v>
@@ -28345,9 +28409,11 @@
         <v>1E-3</v>
       </c>
       <c r="T455" s="9">
-        <v>1.5E-3</v>
-      </c>
-      <c r="U455" s="3"/>
+        <v>2.0000000000000001E-4</v>
+      </c>
+      <c r="U455" s="9">
+        <v>1.5699999999999999E-2</v>
+      </c>
       <c r="V455" s="2" t="s">
         <v>96</v>
       </c>
@@ -28875,7 +28941,9 @@
       <c r="T463" s="4">
         <v>2064.6999999999998</v>
       </c>
-      <c r="U463" s="3"/>
+      <c r="U463" s="4">
+        <v>1636</v>
+      </c>
       <c r="V463" s="2" t="s">
         <v>96</v>
       </c>
@@ -29581,7 +29649,9 @@
       <c r="T474" s="5">
         <v>0</v>
       </c>
-      <c r="U474" s="3"/>
+      <c r="U474" s="5">
+        <v>0</v>
+      </c>
       <c r="V474" s="2" t="s">
         <v>96</v>
       </c>
@@ -29776,7 +29846,7 @@
     <hyperlink ref="A2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.39370078740157499" right="0.39370078740157499" top="0.39370078740157499" bottom="0.39370078740157499" header="0.39370078740157499" footer="0.39370078740157499"/>
-  <pageSetup paperSize="9" scale="69" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" scale="68" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
   <headerFooter alignWithMargins="0"/>
   <drawing r:id="rId3"/>
 </worksheet>

--- a/assets/excel/pl/wskazniki_globalne.xlsx
+++ b/assets/excel/pl/wskazniki_globalne.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\niewiadomskaew\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sidwab\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E29897ED-07EE-4839-AADA-60A27D731FFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C743E3D2-9003-4BAA-A154-2FC0CF24DAB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -949,7 +949,7 @@
     <t>w podziale na</t>
   </si>
   <si>
-    <t>Międzynardowa Organizacja Pracy, Uniwersytet Pensylwanii</t>
+    <t>Międzynarodowa Organizacja Pracy</t>
   </si>
   <si>
     <t>w prawie</t>
@@ -1693,7 +1693,7 @@
     <t>100% rejestracja zgonów</t>
   </si>
   <si>
-    <t>Ostatnia aktualizacja: 28-04-2026, 10:52</t>
+    <t>Ostatnia aktualizacja: 12-05-2026, 12:02</t>
   </si>
 </sst>
 </file>
@@ -3673,7 +3673,9 @@
       <c r="T24" s="6">
         <v>1</v>
       </c>
-      <c r="U24" s="3"/>
+      <c r="U24" s="6">
+        <v>1</v>
+      </c>
       <c r="V24" s="2" t="s">
         <v>56</v>
       </c>
@@ -3729,7 +3731,9 @@
       <c r="T25" s="7">
         <v>0.875</v>
       </c>
-      <c r="U25" s="3"/>
+      <c r="U25" s="7">
+        <v>0.875</v>
+      </c>
       <c r="V25" s="2" t="s">
         <v>56</v>
       </c>
@@ -3785,7 +3789,9 @@
       <c r="T26" s="6">
         <v>16</v>
       </c>
-      <c r="U26" s="3"/>
+      <c r="U26" s="6">
+        <v>16</v>
+      </c>
       <c r="V26" s="2" t="s">
         <v>56</v>
       </c>
@@ -3841,7 +3847,9 @@
       <c r="T27" s="6">
         <v>100</v>
       </c>
-      <c r="U27" s="3"/>
+      <c r="U27" s="6">
+        <v>100</v>
+      </c>
       <c r="V27" s="2" t="s">
         <v>56</v>
       </c>
@@ -17686,7 +17694,9 @@
       <c r="S280" s="5">
         <v>9.5500000000000007</v>
       </c>
-      <c r="T280" s="3"/>
+      <c r="T280" s="5">
+        <v>9.6199999999999992</v>
+      </c>
       <c r="U280" s="3"/>
       <c r="V280" s="2" t="s">
         <v>28</v>
@@ -23661,7 +23671,9 @@
       <c r="T372" s="6">
         <v>1</v>
       </c>
-      <c r="U372" s="3"/>
+      <c r="U372" s="6">
+        <v>1</v>
+      </c>
       <c r="V372" s="2" t="s">
         <v>56</v>
       </c>
@@ -23717,7 +23729,9 @@
       <c r="T373" s="7">
         <v>0.875</v>
       </c>
-      <c r="U373" s="3"/>
+      <c r="U373" s="7">
+        <v>0.875</v>
+      </c>
       <c r="V373" s="2" t="s">
         <v>56</v>
       </c>
@@ -23773,7 +23787,9 @@
       <c r="T374" s="6">
         <v>16</v>
       </c>
-      <c r="U374" s="3"/>
+      <c r="U374" s="6">
+        <v>16</v>
+      </c>
       <c r="V374" s="2" t="s">
         <v>56</v>
       </c>
@@ -23829,7 +23845,9 @@
       <c r="T375" s="6">
         <v>100</v>
       </c>
-      <c r="U375" s="3"/>
+      <c r="U375" s="6">
+        <v>100</v>
+      </c>
       <c r="V375" s="2" t="s">
         <v>56</v>
       </c>
@@ -24671,7 +24689,9 @@
       <c r="T389" s="6">
         <v>1</v>
       </c>
-      <c r="U389" s="3"/>
+      <c r="U389" s="6">
+        <v>1</v>
+      </c>
       <c r="V389" s="2" t="s">
         <v>56</v>
       </c>
@@ -24727,7 +24747,9 @@
       <c r="T390" s="7">
         <v>0.875</v>
       </c>
-      <c r="U390" s="3"/>
+      <c r="U390" s="7">
+        <v>0.875</v>
+      </c>
       <c r="V390" s="2" t="s">
         <v>56</v>
       </c>
@@ -24783,7 +24805,9 @@
       <c r="T391" s="6">
         <v>16</v>
       </c>
-      <c r="U391" s="3"/>
+      <c r="U391" s="6">
+        <v>16</v>
+      </c>
       <c r="V391" s="2" t="s">
         <v>56</v>
       </c>
@@ -24839,7 +24863,9 @@
       <c r="T392" s="6">
         <v>100</v>
       </c>
-      <c r="U392" s="3"/>
+      <c r="U392" s="6">
+        <v>100</v>
+      </c>
       <c r="V392" s="2" t="s">
         <v>56</v>
       </c>

--- a/assets/excel/pl/wskazniki_globalne.xlsx
+++ b/assets/excel/pl/wskazniki_globalne.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sidwab\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\niewiadomskaew\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1EA7781-C5B7-4B28-B799-B3C2F0FCEF5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5514064E-B4F0-460F-81A3-D1789775B8B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cele_1-17" sheetId="1" r:id="rId1"/>
@@ -1684,7 +1684,7 @@
     <t>100% rejestracja zgonów</t>
   </si>
   <si>
-    <t>Ostatnia aktualizacja: 15-05-2026, 12:24</t>
+    <t>Ostatnia aktualizacja: 26-05-2026, 10:02</t>
   </si>
 </sst>
 </file>
@@ -29775,7 +29775,7 @@
     <hyperlink ref="A2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.39370078740157499" right="0.39370078740157499" top="0.39370078740157499" bottom="0.39370078740157499" header="0.39370078740157499" footer="0.39370078740157499"/>
-  <pageSetup paperSize="9" scale="68" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" scale="70" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
   <headerFooter alignWithMargins="0"/>
   <drawing r:id="rId3"/>
 </worksheet>

--- a/assets/excel/pl/wskazniki_globalne.xlsx
+++ b/assets/excel/pl/wskazniki_globalne.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\niewiadomskaew\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sidwab\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5514064E-B4F0-460F-81A3-D1789775B8B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{914850BC-EE4F-4495-B7C1-84FB87EEA27F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1684,7 +1684,7 @@
     <t>100% rejestracja zgonów</t>
   </si>
   <si>
-    <t>Ostatnia aktualizacja: 26-05-2026, 10:02</t>
+    <t>Ostatnia aktualizacja: 23-06-2026, 13:15</t>
   </si>
 </sst>
 </file>
@@ -29775,7 +29775,7 @@
     <hyperlink ref="A2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.39370078740157499" right="0.39370078740157499" top="0.39370078740157499" bottom="0.39370078740157499" header="0.39370078740157499" footer="0.39370078740157499"/>
-  <pageSetup paperSize="9" scale="70" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" scale="68" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
   <headerFooter alignWithMargins="0"/>
   <drawing r:id="rId3"/>
 </worksheet>

--- a/assets/excel/pl/wskazniki_globalne.xlsx
+++ b/assets/excel/pl/wskazniki_globalne.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sidwab\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{914850BC-EE4F-4495-B7C1-84FB87EEA27F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BAA6BBD-A5AF-4358-B86D-F82FFF32E3C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15390" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cele_1-17" sheetId="1" r:id="rId1"/>
@@ -1684,7 +1684,7 @@
     <t>100% rejestracja zgonów</t>
   </si>
   <si>
-    <t>Ostatnia aktualizacja: 23-06-2026, 13:15</t>
+    <t>Ostatnia aktualizacja: 07-07-2026, 14:03</t>
   </si>
 </sst>
 </file>

--- a/assets/excel/pl/wskazniki_globalne.xlsx
+++ b/assets/excel/pl/wskazniki_globalne.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\niewiadomskaew\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35D121FC-C69C-4691-B0D4-2A863F6D7D1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{381A5F1E-0659-4FF8-9249-ACF567FC9305}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1687,7 +1687,7 @@
     <t>100% rejestracja zgonów</t>
   </si>
   <si>
-    <t>Ostatnia aktualizacja: 26-08-2026, 12:35</t>
+    <t>Ostatnia aktualizacja: 01-09-2026, 14:02</t>
   </si>
 </sst>
 </file>
@@ -1789,7 +1789,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
@@ -1813,6 +1813,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="168" fontId="4" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="169" fontId="4" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2257,14 +2260,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="10"/>
-      <c r="B1" s="10"/>
+      <c r="A1" s="11"/>
+      <c r="B1" s="11"/>
     </row>
     <row r="2" spans="1:23" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="10"/>
+      <c r="B2" s="11"/>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
@@ -8590,7 +8593,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="105" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
         <v>152</v>
       </c>
@@ -10510,7 +10513,9 @@
       <c r="U143" s="6">
         <v>1</v>
       </c>
-      <c r="V143" s="3"/>
+      <c r="V143" s="9">
+        <v>1</v>
+      </c>
       <c r="W143" s="2" t="s">
         <v>191</v>
       </c>
@@ -18715,7 +18720,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="290" spans="1:23" ht="45" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A290" s="2" t="s">
         <v>315</v>
       </c>
@@ -20547,7 +20552,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="318" spans="1:23" ht="45" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A318" s="2" t="s">
         <v>347</v>
       </c>
@@ -20616,7 +20621,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="319" spans="1:23" ht="45" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A319" s="2" t="s">
         <v>347</v>
       </c>
@@ -20685,7 +20690,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="320" spans="1:23" ht="72" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:23" ht="63" x14ac:dyDescent="0.25">
       <c r="A320" s="2" t="s">
         <v>347</v>
       </c>
@@ -20754,7 +20759,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="321" spans="1:23" ht="81" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:23" ht="63" x14ac:dyDescent="0.25">
       <c r="A321" s="2" t="s">
         <v>347</v>
       </c>
@@ -20823,7 +20828,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="322" spans="1:23" ht="72" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:23" ht="63" x14ac:dyDescent="0.25">
       <c r="A322" s="2" t="s">
         <v>347</v>
       </c>
@@ -20892,7 +20897,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="323" spans="1:23" ht="81" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:23" ht="72" x14ac:dyDescent="0.25">
       <c r="A323" s="2" t="s">
         <v>347</v>
       </c>
@@ -20961,7 +20966,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="324" spans="1:23" ht="45" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A324" s="2" t="s">
         <v>347</v>
       </c>
@@ -21095,7 +21100,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="326" spans="1:23" ht="81" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:23" ht="63" x14ac:dyDescent="0.25">
       <c r="A326" s="2" t="s">
         <v>347</v>
       </c>
@@ -21617,7 +21622,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="334" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A334" s="2" t="s">
         <v>386</v>
       </c>
@@ -21684,7 +21689,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="335" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A335" s="2" t="s">
         <v>386</v>
       </c>
@@ -21751,7 +21756,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="336" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A336" s="2" t="s">
         <v>386</v>
       </c>
@@ -21818,7 +21823,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="337" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A337" s="2" t="s">
         <v>386</v>
       </c>
@@ -21885,7 +21890,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="338" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A338" s="2" t="s">
         <v>386</v>
       </c>
@@ -21952,7 +21957,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="339" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A339" s="2" t="s">
         <v>386</v>
       </c>
@@ -22019,7 +22024,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="340" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A340" s="2" t="s">
         <v>386</v>
       </c>
@@ -22086,7 +22091,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="341" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A341" s="2" t="s">
         <v>386</v>
       </c>
@@ -22153,7 +22158,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="342" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A342" s="2" t="s">
         <v>386</v>
       </c>
@@ -22220,7 +22225,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="343" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A343" s="2" t="s">
         <v>386</v>
       </c>
@@ -22287,7 +22292,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="344" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A344" s="2" t="s">
         <v>386</v>
       </c>
@@ -22354,7 +22359,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="345" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A345" s="2" t="s">
         <v>386</v>
       </c>
@@ -22421,7 +22426,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="346" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A346" s="2" t="s">
         <v>386</v>
       </c>
@@ -22488,7 +22493,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="347" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A347" s="2" t="s">
         <v>386</v>
       </c>
@@ -22555,7 +22560,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="348" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A348" s="2" t="s">
         <v>386</v>
       </c>
@@ -22622,7 +22627,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="349" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A349" s="2" t="s">
         <v>386</v>
       </c>
@@ -22689,7 +22694,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="350" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A350" s="2" t="s">
         <v>386</v>
       </c>
@@ -22756,7 +22761,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="351" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A351" s="2" t="s">
         <v>386</v>
       </c>
@@ -22823,7 +22828,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="352" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A352" s="2" t="s">
         <v>386</v>
       </c>
@@ -22890,7 +22895,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="353" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A353" s="2" t="s">
         <v>386</v>
       </c>
@@ -22955,7 +22960,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="354" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A354" s="2" t="s">
         <v>386</v>
       </c>
@@ -23022,7 +23027,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="355" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A355" s="2" t="s">
         <v>386</v>
       </c>
@@ -23089,7 +23094,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="356" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A356" s="2" t="s">
         <v>386</v>
       </c>
@@ -23156,7 +23161,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="357" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A357" s="2" t="s">
         <v>386</v>
       </c>
@@ -23223,7 +23228,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="358" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A358" s="2" t="s">
         <v>386</v>
       </c>
@@ -23290,7 +23295,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="359" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A359" s="2" t="s">
         <v>386</v>
       </c>
@@ -23355,7 +23360,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="360" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A360" s="2" t="s">
         <v>386</v>
       </c>
@@ -23420,7 +23425,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="361" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A361" s="2" t="s">
         <v>386</v>
       </c>
@@ -23753,7 +23758,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="366" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A366" s="2" t="s">
         <v>386</v>
       </c>
@@ -23820,7 +23825,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="367" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A367" s="2" t="s">
         <v>386</v>
       </c>
@@ -23887,7 +23892,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="368" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A368" s="2" t="s">
         <v>386</v>
       </c>
@@ -23954,7 +23959,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="369" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A369" s="2" t="s">
         <v>386</v>
       </c>
@@ -24139,7 +24144,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="372" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A372" s="2" t="s">
         <v>386</v>
       </c>
@@ -24198,7 +24203,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="373" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A373" s="2" t="s">
         <v>386</v>
       </c>
@@ -24925,7 +24930,9 @@
       <c r="U384" s="6">
         <v>1</v>
       </c>
-      <c r="V384" s="3"/>
+      <c r="V384" s="9">
+        <v>1</v>
+      </c>
       <c r="W384" s="2" t="s">
         <v>191</v>
       </c>
@@ -25502,7 +25509,9 @@
       <c r="U393" s="6">
         <v>1</v>
       </c>
-      <c r="V393" s="3"/>
+      <c r="V393" s="9">
+        <v>1</v>
+      </c>
       <c r="W393" s="2" t="s">
         <v>191</v>
       </c>
@@ -28934,52 +28943,52 @@
       <c r="E453" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F453" s="9">
+      <c r="F453" s="10">
         <v>2.0999999999999999E-3</v>
       </c>
-      <c r="G453" s="9">
+      <c r="G453" s="10">
         <v>2.5000000000000001E-3</v>
       </c>
-      <c r="H453" s="9">
+      <c r="H453" s="10">
         <v>2.5000000000000001E-3</v>
       </c>
-      <c r="I453" s="9">
+      <c r="I453" s="10">
         <v>9.1999999999999998E-3</v>
       </c>
-      <c r="J453" s="9">
+      <c r="J453" s="10">
         <v>7.7000000000000002E-3</v>
       </c>
-      <c r="K453" s="9">
+      <c r="K453" s="10">
         <v>9.5999999999999992E-3</v>
       </c>
-      <c r="L453" s="9">
+      <c r="L453" s="10">
         <v>1.5900000000000001E-2</v>
       </c>
-      <c r="M453" s="9">
+      <c r="M453" s="10">
         <v>2.8E-3</v>
       </c>
-      <c r="N453" s="9">
+      <c r="N453" s="10">
         <v>1.3299999999999999E-2</v>
       </c>
-      <c r="O453" s="9">
+      <c r="O453" s="10">
         <v>2.5999999999999999E-3</v>
       </c>
-      <c r="P453" s="9">
+      <c r="P453" s="10">
         <v>2.3999999999999998E-3</v>
       </c>
-      <c r="Q453" s="9">
+      <c r="Q453" s="10">
         <v>5.3E-3</v>
       </c>
-      <c r="R453" s="9">
+      <c r="R453" s="10">
         <v>2.2000000000000001E-3</v>
       </c>
-      <c r="S453" s="9">
+      <c r="S453" s="10">
         <v>1E-3</v>
       </c>
-      <c r="T453" s="9">
+      <c r="T453" s="10">
         <v>2.0000000000000001E-4</v>
       </c>
-      <c r="U453" s="9">
+      <c r="U453" s="10">
         <v>1.5699999999999999E-2</v>
       </c>
       <c r="V453" s="3"/>
@@ -30451,10 +30460,10 @@
     </row>
     <row r="476" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="477" spans="1:23" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A477" s="12" t="s">
+      <c r="A477" s="13" t="s">
         <v>552</v>
       </c>
-      <c r="B477" s="10"/>
+      <c r="B477" s="11"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:B3" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
